--- a/assets/Tabelas de referência/Itens.xlsx
+++ b/assets/Tabelas de referência/Itens.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5aa5356bde13b7c5/Área de Trabalho/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\TransferToolMobile\TransferTool\assets\Tabelas de referência\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{CC3D890B-29DC-42FA-9E37-ED9EC722BF24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B5E738B-2FA0-4AF8-9B88-E6E78F932D85}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F988D043-39AB-4413-98D6-25100C7E22E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Report!$A$2:$B$35</definedName>
+    <definedName name="__bookmark_1">Report!$A$2:$B$33</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
     <t>Produto - Código</t>
   </si>
@@ -73,9 +73,6 @@
     <t>ATUM</t>
   </si>
   <si>
-    <t>LEITE EM PÓ INSTANTÂNEO - INTEGRAL</t>
-  </si>
-  <si>
     <t>LENTILHA</t>
   </si>
   <si>
@@ -130,9 +127,6 @@
     <t>ALECRIM</t>
   </si>
   <si>
-    <t>COPO DE ÁGUA MINERAL - 200 ML</t>
-  </si>
-  <si>
     <t>BALDE MULTIUSO (10 A 12 LITROS)</t>
   </si>
   <si>
@@ -251,6 +245,69 @@
   </si>
   <si>
     <t>RALADOR MANUAL</t>
+  </si>
+  <si>
+    <t>ARROZ ORGÂNICO PARBOILIZADO</t>
+  </si>
+  <si>
+    <t>BISCOITO DOCE - TIPO MAISENA</t>
+  </si>
+  <si>
+    <t>BISCOITO MARIA INTEGRAL CHOCOLATE</t>
+  </si>
+  <si>
+    <t>CAFÉ SOLÚVEL</t>
+  </si>
+  <si>
+    <t>COLORAU</t>
+  </si>
+  <si>
+    <t>FARINHA DE TRIGO INTEGRAL</t>
+  </si>
+  <si>
+    <t>FERMENTO BIOLÓGICO</t>
+  </si>
+  <si>
+    <t>FERMENTO EM PÓ - QUÍMICO</t>
+  </si>
+  <si>
+    <t>FÓRMULA INFANTIL DE PARTIDA PARA LACTENTES DE 0 A 6 MESES</t>
+  </si>
+  <si>
+    <t>LEITE EM PÓ - SEM LACTOSE</t>
+  </si>
+  <si>
+    <t>LEITEIRA</t>
+  </si>
+  <si>
+    <t>MACARRÃO - ESPAGUETE</t>
+  </si>
+  <si>
+    <t>MACARRÃO - PARAFUSO INTEGRAL</t>
+  </si>
+  <si>
+    <t>MILHO PIPOCA</t>
+  </si>
+  <si>
+    <t>SACOS PLÁSTICOS PARA ALIMENTOS (BOBINA) - 10KG</t>
+  </si>
+  <si>
+    <t>CHOCOLATE EM PO SOLÚVEL - 200G</t>
+  </si>
+  <si>
+    <t>8875, 12494</t>
+  </si>
+  <si>
+    <t>SUCO DE UVA TINTO INTEGRAL - 1L</t>
+  </si>
+  <si>
+    <t>SUCO CAIXINHA UVA</t>
+  </si>
+  <si>
+    <t>SUCO CAIXINHA LARANJA E MAÇÃ</t>
+  </si>
+  <si>
+    <t>Depósito de origem</t>
   </si>
 </sst>
 </file>
@@ -298,13 +355,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -329,7 +389,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -365,11 +425,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8966D0F2-4673-4B23-BFE9-8FC8FF9A7AFA}" name="Tabela2" displayName="Tabela2" ref="A1:B75" totalsRowShown="0">
-  <autoFilter ref="A1:B75" xr:uid="{8966D0F2-4673-4B23-BFE9-8FC8FF9A7AFA}"/>
-  <tableColumns count="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8966D0F2-4673-4B23-BFE9-8FC8FF9A7AFA}" name="Tabela2" displayName="Tabela2" ref="A1:C92" totalsRowShown="0">
+  <autoFilter ref="A1:C92" xr:uid="{8966D0F2-4673-4B23-BFE9-8FC8FF9A7AFA}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C92">
+    <sortCondition ref="C1:C92"/>
+  </sortState>
+  <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{621186F0-1773-4C3B-8EAB-49AEDA74FC59}" name="Produto - Código" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{16405913-667D-4554-872C-BCD9571BEF45}" name="Produto - Descrição" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{7E10E046-6999-4AAE-80A0-973479E0E285}" name="Depósito de origem"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -672,611 +736,1092 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5212EF77-5BBA-48E5-BD33-F106FF63EC9B}">
-  <dimension ref="A1:B75"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
     <col min="2" max="2" width="54.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
+        <v>25510</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>36706</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>8147</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>10091</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>2201</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+      <c r="C6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>3451</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>27874</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>2203</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+      <c r="C9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>13455</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>28848</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>2206</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>16133</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>29427</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14944</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>6840</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>9523</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>28052</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
         <v>2214</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="C20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
         <v>2215</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+      <c r="C21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
         <v>2216</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+      <c r="C22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>28856</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
         <v>2217</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B24" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+      <c r="C24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
         <v>2218</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+      <c r="C25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>12614</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>24534</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>29319</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>34415</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>34416</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>23615</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>29285</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>7513</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>29431</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
         <v>2223</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B35" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+      <c r="C35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>2999</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
         <v>2224</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>36708</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C38">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
         <v>2227</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B39" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+      <c r="C39">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>29528</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>40306</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C41">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>34417</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
         <v>2235</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B43" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+      <c r="C43">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>29433</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C44">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>34518</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>32805</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C46">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
         <v>2238</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B47" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>2240</v>
-      </c>
-      <c r="B14" s="2" t="s">
+      <c r="C47">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>29299</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C48">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>4861</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>3451</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>6615</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>7513</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>8147</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>8875</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>13455</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>14944</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>23615</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>25510</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>27874</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>28052</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>29319</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <v>29427</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
-        <v>29431</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
-        <v>29433</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
-        <v>29528</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
-        <v>34416</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
-        <v>34417</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
-        <v>34518</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
-        <v>36706</v>
-      </c>
-      <c r="B34" s="2" t="s">
+      <c r="C49">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>33621</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C50">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>33622</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C51">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>8564</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C52">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>37353</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C53">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>2888</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C54">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>5573</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C55">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>33493</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C56">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>777</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
-        <v>38355</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
-        <v>777</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
-        <v>2888</v>
-      </c>
-      <c r="B37" s="2" t="s">
+      <c r="C57">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>32929</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C58">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>23386</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C59">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>6144</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
-        <v>5573</v>
-      </c>
-      <c r="B38" s="2" t="s">
+      <c r="C60">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>14811</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C61">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>37354</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C62">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>37355</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C63">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>37357</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C64">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>7560</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C65">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>31973</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C66">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>8784</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C67">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>37362</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C68">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>37363</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C69">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>37366</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C70">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>37368</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C71">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>37369</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C72">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>3343</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C73">
+        <v>69</v>
+      </c>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>37371</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C74">
+        <v>69</v>
+      </c>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>37372</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C75">
+        <v>69</v>
+      </c>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>34544</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C76">
+        <v>69</v>
+      </c>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>23875</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C77">
+        <v>69</v>
+      </c>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>32991</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C78">
+        <v>69</v>
+      </c>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>37373</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C79">
+        <v>69</v>
+      </c>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>37376</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C80">
+        <v>69</v>
+      </c>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>7539</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
-        <v>6144</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
-        <v>7539</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
-        <v>7560</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="1">
-        <v>8564</v>
-      </c>
-      <c r="B42" s="2" t="s">
+      <c r="C81">
+        <v>69</v>
+      </c>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>37379</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C82">
+        <v>69</v>
+      </c>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>37381</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C83">
+        <v>69</v>
+      </c>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>37382</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C84">
+        <v>69</v>
+      </c>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>37383</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C85">
+        <v>69</v>
+      </c>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>12548</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="1">
-        <v>8784</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="1">
-        <v>12548</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="1">
-        <v>14811</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="1">
-        <v>23386</v>
-      </c>
-      <c r="B46" s="2" t="s">
+      <c r="C86">
+        <v>69</v>
+      </c>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>32994</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C87">
+        <v>69</v>
+      </c>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>37384</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C88">
+        <v>69</v>
+      </c>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>30667</v>
+      </c>
+      <c r="B89" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="1">
-        <v>23875</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="1">
-        <v>30667</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="1">
-        <v>31973</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="1">
-        <v>32805</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="1">
-        <v>32929</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="1">
-        <v>32991</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="1">
-        <v>32994</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="1">
-        <v>33493</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="1">
-        <v>34544</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="1">
-        <v>37353</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="1">
-        <v>37354</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="1">
-        <v>37355</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
-        <v>37357</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="1">
-        <v>37362</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
-        <v>37363</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="1">
-        <v>37366</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="1">
-        <v>37368</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="1">
-        <v>37369</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="1">
-        <v>37371</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="1">
-        <v>37372</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="1">
-        <v>37373</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="1">
-        <v>37376</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="1">
-        <v>37379</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="1">
-        <v>37381</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="1">
-        <v>37382</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="1">
-        <v>37383</v>
-      </c>
-      <c r="B72" s="2" t="s">
+      <c r="C89">
+        <v>69</v>
+      </c>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>37386</v>
+      </c>
+      <c r="B90" s="3" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="1">
-        <v>37384</v>
-      </c>
-      <c r="B73" s="2" t="s">
+      <c r="C90">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>37387</v>
+      </c>
+      <c r="B91" s="3" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="1">
-        <v>37386</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="1">
-        <v>37387</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>75</v>
+      <c r="C91">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>35192</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C92">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/assets/Tabelas de referência/Itens.xlsx
+++ b/assets/Tabelas de referência/Itens.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\TransferToolMobile\TransferTool\assets\Tabelas de referência\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\TransferToolMobile\TransferTool Mobile\assets\Tabelas de referência\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F988D043-39AB-4413-98D6-25100C7E22E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37530BC4-F2F7-4DFD-8E59-710DC925847C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="2" r:id="rId1"/>
@@ -79,9 +79,6 @@
     <t>AMIDO DE MILHO</t>
   </si>
   <si>
-    <t>EXTRATO TOMATE</t>
-  </si>
-  <si>
     <t>BISCOITO DOCE - SABOR LEITE</t>
   </si>
   <si>
@@ -115,9 +112,6 @@
     <t>MANJERICÃO</t>
   </si>
   <si>
-    <t>FÓRMULA INFANTIL DE SEGUIMENTO - PARA LACTENTES DE 6 A 12 MESES</t>
-  </si>
-  <si>
     <t>MILHO VERDE</t>
   </si>
   <si>
@@ -250,12 +244,6 @@
     <t>ARROZ ORGÂNICO PARBOILIZADO</t>
   </si>
   <si>
-    <t>BISCOITO DOCE - TIPO MAISENA</t>
-  </si>
-  <si>
-    <t>BISCOITO MARIA INTEGRAL CHOCOLATE</t>
-  </si>
-  <si>
     <t>CAFÉ SOLÚVEL</t>
   </si>
   <si>
@@ -268,12 +256,6 @@
     <t>FERMENTO BIOLÓGICO</t>
   </si>
   <si>
-    <t>FERMENTO EM PÓ - QUÍMICO</t>
-  </si>
-  <si>
-    <t>FÓRMULA INFANTIL DE PARTIDA PARA LACTENTES DE 0 A 6 MESES</t>
-  </si>
-  <si>
     <t>LEITE EM PÓ - SEM LACTOSE</t>
   </si>
   <si>
@@ -308,6 +290,24 @@
   </si>
   <si>
     <t>Depósito de origem</t>
+  </si>
+  <si>
+    <t>BISCOITO DOCE - SABORMAISENA</t>
+  </si>
+  <si>
+    <t>BISCOITO MARIA INTEGRAL - SABOR CHOCOLATE</t>
+  </si>
+  <si>
+    <t>EXTRATO DE TOMATE</t>
+  </si>
+  <si>
+    <t>FERMENTO QUÍMICO</t>
+  </si>
+  <si>
+    <t>0 A 6 MESES - FÓRMULA INFANTIL DE PARTIDA PARA LACTENTES</t>
+  </si>
+  <si>
+    <t>6 A 12 MESES - FÓRMULA INFANTIL DE SEGUIMENTO - PARA LACTENTES</t>
   </si>
 </sst>
 </file>
@@ -752,7 +752,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -760,7 +760,7 @@
         <v>25510</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -771,7 +771,7 @@
         <v>36706</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -793,7 +793,7 @@
         <v>10091</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C5">
         <v>10</v>
@@ -826,7 +826,7 @@
         <v>27874</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8">
         <v>10</v>
@@ -848,7 +848,7 @@
         <v>13455</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10">
         <v>10</v>
@@ -859,7 +859,7 @@
         <v>28848</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -870,7 +870,7 @@
         <v>2206</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="C12">
         <v>10</v>
@@ -881,7 +881,7 @@
         <v>16133</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C13">
         <v>10</v>
@@ -892,7 +892,7 @@
         <v>29427</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14">
         <v>10</v>
@@ -903,7 +903,7 @@
         <v>14944</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C15">
         <v>10</v>
@@ -914,7 +914,7 @@
         <v>6840</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C16">
         <v>10</v>
@@ -925,7 +925,7 @@
         <v>9523</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C17">
         <v>10</v>
@@ -936,7 +936,7 @@
         <v>28052</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18">
         <v>10</v>
@@ -944,10 +944,10 @@
     </row>
     <row r="19" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="C19">
         <v>10</v>
@@ -991,7 +991,7 @@
         <v>28856</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C23">
         <v>10</v>
@@ -1024,7 +1024,7 @@
         <v>12614</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C26">
         <v>10</v>
@@ -1035,7 +1035,7 @@
         <v>24534</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="C27">
         <v>10</v>
@@ -1046,7 +1046,7 @@
         <v>29319</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C28">
         <v>10</v>
@@ -1057,7 +1057,7 @@
         <v>34415</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="C29">
         <v>10</v>
@@ -1068,7 +1068,7 @@
         <v>34416</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="C30">
         <v>10</v>
@@ -1079,7 +1079,7 @@
         <v>23615</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C31">
         <v>10</v>
@@ -1090,7 +1090,7 @@
         <v>29285</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C32">
         <v>10</v>
@@ -1112,7 +1112,7 @@
         <v>29431</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C34">
         <v>10</v>
@@ -1134,7 +1134,7 @@
         <v>2999</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C36">
         <v>10</v>
@@ -1156,7 +1156,7 @@
         <v>36708</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C38">
         <v>10</v>
@@ -1178,7 +1178,7 @@
         <v>29528</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C40">
         <v>10</v>
@@ -1189,7 +1189,7 @@
         <v>40306</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C41">
         <v>10</v>
@@ -1200,7 +1200,7 @@
         <v>34417</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C42">
         <v>10</v>
@@ -1222,7 +1222,7 @@
         <v>29433</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C44">
         <v>10</v>
@@ -1233,7 +1233,7 @@
         <v>34518</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C45">
         <v>10</v>
@@ -1244,7 +1244,7 @@
         <v>32805</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C46">
         <v>10</v>
@@ -1266,7 +1266,7 @@
         <v>29299</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C48">
         <v>10</v>
@@ -1288,7 +1288,7 @@
         <v>33621</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C50">
         <v>10</v>
@@ -1299,7 +1299,7 @@
         <v>33622</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C51">
         <v>10</v>
@@ -1310,7 +1310,7 @@
         <v>8564</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C52">
         <v>69</v>
@@ -1321,7 +1321,7 @@
         <v>37353</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C53">
         <v>69</v>
@@ -1332,7 +1332,7 @@
         <v>2888</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C54">
         <v>69</v>
@@ -1343,7 +1343,7 @@
         <v>5573</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C55">
         <v>69</v>
@@ -1354,7 +1354,7 @@
         <v>33493</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C56">
         <v>69</v>
@@ -1365,7 +1365,7 @@
         <v>777</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C57">
         <v>69</v>
@@ -1376,7 +1376,7 @@
         <v>32929</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C58">
         <v>69</v>
@@ -1387,7 +1387,7 @@
         <v>23386</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C59">
         <v>69</v>
@@ -1398,7 +1398,7 @@
         <v>6144</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C60">
         <v>69</v>
@@ -1409,7 +1409,7 @@
         <v>14811</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C61">
         <v>69</v>
@@ -1420,7 +1420,7 @@
         <v>37354</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C62">
         <v>69</v>
@@ -1431,7 +1431,7 @@
         <v>37355</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C63">
         <v>69</v>
@@ -1442,7 +1442,7 @@
         <v>37357</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C64">
         <v>69</v>
@@ -1453,7 +1453,7 @@
         <v>7560</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C65">
         <v>69</v>
@@ -1464,7 +1464,7 @@
         <v>31973</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C66">
         <v>69</v>
@@ -1475,7 +1475,7 @@
         <v>8784</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C67">
         <v>69</v>
@@ -1486,7 +1486,7 @@
         <v>37362</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C68">
         <v>69</v>
@@ -1497,7 +1497,7 @@
         <v>37363</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C69">
         <v>69</v>
@@ -1508,7 +1508,7 @@
         <v>37366</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1519,7 +1519,7 @@
         <v>37368</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C71">
         <v>69</v>
@@ -1530,7 +1530,7 @@
         <v>37369</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C72">
         <v>69</v>
@@ -1541,7 +1541,7 @@
         <v>3343</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C73">
         <v>69</v>
@@ -1556,7 +1556,7 @@
         <v>37371</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C74">
         <v>69</v>
@@ -1571,7 +1571,7 @@
         <v>37372</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C75">
         <v>69</v>
@@ -1586,7 +1586,7 @@
         <v>34544</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C76">
         <v>69</v>
@@ -1601,7 +1601,7 @@
         <v>23875</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C77">
         <v>69</v>
@@ -1616,7 +1616,7 @@
         <v>32991</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C78">
         <v>69</v>
@@ -1631,7 +1631,7 @@
         <v>37373</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C79">
         <v>69</v>
@@ -1646,7 +1646,7 @@
         <v>37376</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C80">
         <v>69</v>
@@ -1661,7 +1661,7 @@
         <v>7539</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C81">
         <v>69</v>
@@ -1676,7 +1676,7 @@
         <v>37379</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C82">
         <v>69</v>
@@ -1691,7 +1691,7 @@
         <v>37381</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C83">
         <v>69</v>
@@ -1706,7 +1706,7 @@
         <v>37382</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C84">
         <v>69</v>
@@ -1721,7 +1721,7 @@
         <v>37383</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C85">
         <v>69</v>
@@ -1736,7 +1736,7 @@
         <v>12548</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C86">
         <v>69</v>
@@ -1751,7 +1751,7 @@
         <v>32994</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C87">
         <v>69</v>
@@ -1766,7 +1766,7 @@
         <v>37384</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C88">
         <v>69</v>
@@ -1781,7 +1781,7 @@
         <v>30667</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C89">
         <v>69</v>
@@ -1796,7 +1796,7 @@
         <v>37386</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C90">
         <v>69</v>
@@ -1807,7 +1807,7 @@
         <v>37387</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C91">
         <v>69</v>
@@ -1818,7 +1818,7 @@
         <v>35192</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C92">
         <v>69</v>
